--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.17948530269091</v>
+        <v>10.26666636168727</v>
       </c>
       <c r="D2" t="n">
-        <v>59.64871932842656</v>
+        <v>9.692916890869316</v>
       </c>
       <c r="E2" t="n">
-        <v>27.66450034732567</v>
+        <v>4.495481306440421</v>
       </c>
       <c r="F2" t="n">
-        <v>28.06510778092816</v>
+        <v>4.560580014400826</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.32513758079568</v>
+        <v>3.627834856879297</v>
       </c>
       <c r="D3" t="n">
-        <v>22.24751966534624</v>
+        <v>3.615221945618765</v>
       </c>
       <c r="E3" t="n">
-        <v>27.66450034732567</v>
+        <v>4.495481306440421</v>
       </c>
       <c r="F3" t="n">
-        <v>28.06510778092816</v>
+        <v>4.560580014400826</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.56085945578851</v>
+        <v>4.641139661565632</v>
       </c>
       <c r="D4" t="n">
-        <v>25.12038493442792</v>
+        <v>4.082062551844538</v>
       </c>
       <c r="E4" t="n">
-        <v>27.66450034732567</v>
+        <v>4.495481306440421</v>
       </c>
       <c r="F4" t="n">
-        <v>28.06510778092816</v>
+        <v>4.560580014400826</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>90.84220963610873</v>
+        <v>14.76185906586767</v>
       </c>
       <c r="D5" t="n">
-        <v>90.85873745139645</v>
+        <v>14.76454483585192</v>
       </c>
       <c r="E5" t="n">
-        <v>27.66450034732567</v>
+        <v>4.495481306440421</v>
       </c>
       <c r="F5" t="n">
-        <v>28.06510778092816</v>
+        <v>4.560580014400826</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
